--- a/docs/reference-documents/Registers_Compare_324_328.xlsx
+++ b/docs/reference-documents/Registers_Compare_324_328.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD45F39-AA0E-4F9D-8CA8-D30014E544E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Register comparison" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="122211"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="48">
   <si>
     <t>register 1</t>
   </si>
@@ -123,11 +129,95 @@
   <si>
     <t>Information from iom328pb.h</t>
   </si>
+  <si>
+    <t>PORTA</t>
+  </si>
+  <si>
+    <t>UCSR0A</t>
+  </si>
+  <si>
+    <t>RXC</t>
+  </si>
+  <si>
+    <t>TXC</t>
+  </si>
+  <si>
+    <t>UDRE</t>
+  </si>
+  <si>
+    <t>FE</t>
+  </si>
+  <si>
+    <t>DOR</t>
+  </si>
+  <si>
+    <t>UPE</t>
+  </si>
+  <si>
+    <t>U2X</t>
+  </si>
+  <si>
+    <t>MPCM</t>
+  </si>
+  <si>
+    <t>TCCR0A</t>
+  </si>
+  <si>
+    <t>COM0A1</t>
+  </si>
+  <si>
+    <t>COM0A0</t>
+  </si>
+  <si>
+    <t>COM0B1</t>
+  </si>
+  <si>
+    <t>COM0B0</t>
+  </si>
+  <si>
+    <t>Dummy3</t>
+  </si>
+  <si>
+    <t>Dummy2</t>
+  </si>
+  <si>
+    <t>WGM01</t>
+  </si>
+  <si>
+    <t>WGM00</t>
+  </si>
+  <si>
+    <t>PORTA7</t>
+  </si>
+  <si>
+    <t>PORTA6</t>
+  </si>
+  <si>
+    <t>PORTA5</t>
+  </si>
+  <si>
+    <t>PORTA4</t>
+  </si>
+  <si>
+    <t>PORTA3</t>
+  </si>
+  <si>
+    <t>PORTA2</t>
+  </si>
+  <si>
+    <t>PORTA1</t>
+  </si>
+  <si>
+    <t>PORTA0</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -225,6 +315,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -237,8 +329,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -257,9 +347,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -297,9 +387,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -334,7 +424,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -369,7 +459,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -542,76 +632,76 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" customWidth="1"/>
-    <col min="6" max="7" width="7.85546875" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" customWidth="1"/>
+    <col min="5" max="5" width="6.5546875" customWidth="1"/>
+    <col min="6" max="7" width="7.88671875" customWidth="1"/>
     <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="7.140625" customWidth="1"/>
-    <col min="10" max="10" width="7.85546875" customWidth="1"/>
-    <col min="11" max="11" width="8.85546875" customWidth="1"/>
-    <col min="12" max="12" width="2.140625" customWidth="1"/>
-    <col min="13" max="13" width="13.28515625" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+    <col min="9" max="9" width="7.109375" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" customWidth="1"/>
+    <col min="12" max="12" width="2.109375" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="M2" s="8" t="s">
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="M2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="O2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="P2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
       <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
@@ -636,9 +726,9 @@
       <c r="K3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
       <c r="P3" s="5" t="s">
         <v>11</v>
       </c>
@@ -664,20 +754,40 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="M4" s="4" t="s">
         <v>0</v>
       </c>
@@ -692,20 +802,40 @@
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
+      <c r="B5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="M5" s="4" t="s">
         <v>1</v>
       </c>
@@ -719,20 +849,40 @@
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
+      <c r="B6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="M6" s="4" t="s">
         <v>2</v>
       </c>
@@ -747,58 +897,58 @@
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="M7" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="M8" s="8" t="s">
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="M8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N8" s="8" t="s">
+      <c r="N8" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="8" t="s">
+      <c r="O8" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="P8" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="9"/>
-      <c r="U8" s="9"/>
-      <c r="V8" s="9"/>
-      <c r="W8" s="9"/>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
+      <c r="V8" s="11"/>
+      <c r="W8" s="11"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
       <c r="D9" s="7" t="s">
         <v>11</v>
       </c>
@@ -823,9 +973,9 @@
       <c r="K9" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
       <c r="P9" s="6" t="s">
         <v>11</v>
       </c>
@@ -851,20 +1001,40 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="B10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="M10" s="4" t="s">
         <v>0</v>
       </c>
@@ -879,20 +1049,40 @@
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="M11" s="4" t="s">
         <v>1</v>
       </c>
@@ -906,20 +1096,40 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="B12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="M12" s="4" t="s">
         <v>2</v>
       </c>
@@ -934,58 +1144,58 @@
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="M13" s="12" t="s">
+      <c r="M13" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="M14" s="8" t="s">
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="M14" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N14" s="8" t="s">
+      <c r="N14" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="8" t="s">
+      <c r="O14" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="P14" s="9" t="s">
+      <c r="P14" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="9"/>
-      <c r="U14" s="9"/>
-      <c r="V14" s="9"/>
-      <c r="W14" s="9"/>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="11"/>
+      <c r="W14" s="11"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
       <c r="D15" s="7" t="s">
         <v>11</v>
       </c>
@@ -1010,9 +1220,9 @@
       <c r="K15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
       <c r="P15" s="6" t="s">
         <v>11</v>
       </c>
@@ -1038,20 +1248,40 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
+      <c r="B16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="M16" s="4" t="s">
         <v>0</v>
       </c>
@@ -1066,20 +1296,40 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
+      <c r="B17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="M17" s="4" t="s">
         <v>1</v>
       </c>
@@ -1093,20 +1343,40 @@
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="M18" s="4" t="s">
         <v>2</v>
       </c>
@@ -1123,6 +1393,22 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:K14"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:K8"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="P2:W2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:K2"/>
     <mergeCell ref="M8:M9"/>
     <mergeCell ref="N8:N9"/>
     <mergeCell ref="O8:O9"/>
@@ -1131,22 +1417,6 @@
     <mergeCell ref="N14:N15"/>
     <mergeCell ref="O14:O15"/>
     <mergeCell ref="P14:W14"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:W2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:K2"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:K8"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:K14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>

--- a/docs/reference-documents/Registers_Compare_324_328.xlsx
+++ b/docs/reference-documents/Registers_Compare_324_328.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD45F39-AA0E-4F9D-8CA8-D30014E544E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB528698-56F1-4D9F-A211-13E851AE259C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11376" yWindow="0" windowWidth="11760" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Register comparison" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="48">
   <si>
     <t>register 1</t>
   </si>
@@ -791,16 +791,36 @@
       <c r="M4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
+      <c r="N4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O4" s="3">
+        <v>1</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -839,15 +859,36 @@
       <c r="M5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
+      <c r="N5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" s="3">
+        <v>1</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -886,16 +927,36 @@
       <c r="M6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
+      <c r="N6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="W6" s="3" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
@@ -1038,16 +1099,36 @@
       <c r="M10" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
+      <c r="N10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
@@ -1086,15 +1167,36 @@
       <c r="M11" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
+      <c r="N11" t="s">
+        <v>30</v>
+      </c>
+      <c r="O11" s="3">
+        <v>1</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="U11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
@@ -1133,16 +1235,36 @@
       <c r="M12" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
+      <c r="N12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
@@ -1285,16 +1407,36 @@
       <c r="M16" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
+      <c r="N16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" s="3">
+        <v>1</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="U16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="W16" s="3" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
@@ -1333,7 +1475,12 @@
       <c r="M17" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="O17" s="3"/>
+      <c r="N17" t="s">
+        <v>30</v>
+      </c>
+      <c r="O17" s="3">
+        <v>1</v>
+      </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
@@ -1380,16 +1527,36 @@
       <c r="M18" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
+      <c r="N18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="24">

--- a/docs/reference-documents/Registers_Compare_324_328.xlsx
+++ b/docs/reference-documents/Registers_Compare_324_328.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D165C88-19D1-4971-9880-34C1B5CF7C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Register comparison" sheetId="1" r:id="rId1"/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="60">
   <si>
     <t>register 1</t>
   </si>
@@ -123,12 +124,132 @@
   <si>
     <t>Information from iom328pb.h</t>
   </si>
+  <si>
+    <t>TWAMR1</t>
+  </si>
+  <si>
+    <t>0xDD</t>
+  </si>
+  <si>
+    <t>TWAM16</t>
+  </si>
+  <si>
+    <t>TWAM15</t>
+  </si>
+  <si>
+    <t>TWAM14</t>
+  </si>
+  <si>
+    <t>TWAM13</t>
+  </si>
+  <si>
+    <t>TWAM12</t>
+  </si>
+  <si>
+    <t>TWAM11</t>
+  </si>
+  <si>
+    <t>TWAM10</t>
+  </si>
+  <si>
+    <t>Dummy0</t>
+  </si>
+  <si>
+    <t>TWAM[6]</t>
+  </si>
+  <si>
+    <t>TWAM[5]</t>
+  </si>
+  <si>
+    <t>TWAM[4]</t>
+  </si>
+  <si>
+    <t>TWAM[3]</t>
+  </si>
+  <si>
+    <t>TWAM[2]</t>
+  </si>
+  <si>
+    <t>TWAM[1]</t>
+  </si>
+  <si>
+    <t>TWAM[0]</t>
+  </si>
+  <si>
+    <t>ASSR</t>
+  </si>
+  <si>
+    <t>0xB6</t>
+  </si>
+  <si>
+    <t>Dummy7</t>
+  </si>
+  <si>
+    <t>EXCLK</t>
+  </si>
+  <si>
+    <t>AS2</t>
+  </si>
+  <si>
+    <t>TCN2UB</t>
+  </si>
+  <si>
+    <t>OCR2AUB</t>
+  </si>
+  <si>
+    <t>OCR2BUB</t>
+  </si>
+  <si>
+    <t>TCR2AUB</t>
+  </si>
+  <si>
+    <t>TCR2BUB</t>
+  </si>
+  <si>
+    <t>ADCSRA</t>
+  </si>
+  <si>
+    <t>0x7A</t>
+  </si>
+  <si>
+    <t>ADEN</t>
+  </si>
+  <si>
+    <t>ADSC</t>
+  </si>
+  <si>
+    <t>ADATE</t>
+  </si>
+  <si>
+    <t>ADIF</t>
+  </si>
+  <si>
+    <t>ADIE</t>
+  </si>
+  <si>
+    <t>ADPS2</t>
+  </si>
+  <si>
+    <t>ADPS1</t>
+  </si>
+  <si>
+    <t>ADPS0</t>
+  </si>
+  <si>
+    <t>ADPS2[2]</t>
+  </si>
+  <si>
+    <t>ADPS2[1]</t>
+  </si>
+  <si>
+    <t>ADPS2[0]</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,6 +277,12 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -208,7 +335,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -219,12 +346,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -237,8 +359,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -257,9 +377,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -297,9 +417,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -334,7 +454,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -369,7 +489,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -542,76 +662,76 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" customWidth="1"/>
-    <col min="6" max="7" width="7.85546875" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" customWidth="1"/>
+    <col min="5" max="5" width="6.5546875" customWidth="1"/>
+    <col min="6" max="7" width="7.88671875" customWidth="1"/>
     <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="7.140625" customWidth="1"/>
-    <col min="10" max="10" width="7.85546875" customWidth="1"/>
-    <col min="11" max="11" width="8.85546875" customWidth="1"/>
-    <col min="12" max="12" width="2.140625" customWidth="1"/>
-    <col min="13" max="13" width="13.28515625" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+    <col min="9" max="9" width="7.109375" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" customWidth="1"/>
+    <col min="12" max="12" width="2.109375" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="M2" s="8" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="M2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="O2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="P2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
+      <c r="V2" s="8"/>
+      <c r="W2" s="8"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
       <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
@@ -636,9 +756,9 @@
       <c r="K3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
       <c r="P3" s="5" t="s">
         <v>11</v>
       </c>
@@ -664,20 +784,40 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="M4" s="4" t="s">
         <v>0</v>
       </c>
@@ -692,20 +832,40 @@
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
+      <c r="B5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="M5" s="4" t="s">
         <v>1</v>
       </c>
@@ -719,20 +879,40 @@
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
+      <c r="B6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="M6" s="4" t="s">
         <v>2</v>
       </c>
@@ -747,123 +927,141 @@
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="M7" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="M8" s="8" t="s">
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="M8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="N8" s="8" t="s">
+      <c r="N8" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="8" t="s">
+      <c r="O8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="P8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="9"/>
-      <c r="U8" s="9"/>
-      <c r="V8" s="9"/>
-      <c r="W8" s="9"/>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="7" t="s">
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="K9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="6" t="s">
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="Q9" s="6" t="s">
+      <c r="Q9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="R9" s="6" t="s">
+      <c r="R9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="S9" s="6" t="s">
+      <c r="S9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="T9" s="6" t="s">
+      <c r="T9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="U9" s="6" t="s">
+      <c r="U9" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="V9" s="6" t="s">
+      <c r="V9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="W9" s="6" t="s">
+      <c r="W9" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
+      <c r="B10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="K10" s="3"/>
       <c r="M10" s="4" t="s">
         <v>0</v>
@@ -879,20 +1077,38 @@
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="E11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="M11" s="4" t="s">
         <v>1</v>
       </c>
@@ -906,20 +1122,40 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="B12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="M12" s="4" t="s">
         <v>2</v>
       </c>
@@ -934,123 +1170,141 @@
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="M13" s="12" t="s">
+      <c r="M13" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="M14" s="8" t="s">
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="M14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="N14" s="8" t="s">
+      <c r="N14" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="8" t="s">
+      <c r="O14" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="P14" s="9" t="s">
+      <c r="P14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="9"/>
-      <c r="U14" s="9"/>
-      <c r="V14" s="9"/>
-      <c r="W14" s="9"/>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="7" t="s">
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8"/>
+      <c r="V14" s="8"/>
+      <c r="W14" s="8"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="7" t="s">
+      <c r="K15" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="6" t="s">
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="Q15" s="6" t="s">
+      <c r="Q15" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="6" t="s">
+      <c r="R15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="S15" s="6" t="s">
+      <c r="S15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="s">
+      <c r="T15" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="U15" s="6" t="s">
+      <c r="U15" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="V15" s="6" t="s">
+      <c r="V15" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="W15" s="6" t="s">
+      <c r="W15" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
+      <c r="B16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="K16" s="3"/>
       <c r="M16" s="4" t="s">
         <v>0</v>
@@ -1066,20 +1320,38 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
+      <c r="B17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
+      <c r="E17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="M17" s="4" t="s">
         <v>1</v>
       </c>
@@ -1093,20 +1365,40 @@
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="M18" s="4" t="s">
         <v>2</v>
       </c>
@@ -1123,6 +1415,22 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:K14"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:K8"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="P2:W2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:K2"/>
     <mergeCell ref="M8:M9"/>
     <mergeCell ref="N8:N9"/>
     <mergeCell ref="O8:O9"/>
@@ -1131,23 +1439,8 @@
     <mergeCell ref="N14:N15"/>
     <mergeCell ref="O14:O15"/>
     <mergeCell ref="P14:W14"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:W2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:K2"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:K8"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:K14"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>
 </worksheet>

--- a/docs/reference-documents/Registers_Compare_324_328.xlsx
+++ b/docs/reference-documents/Registers_Compare_324_328.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D165C88-19D1-4971-9880-34C1B5CF7C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970AF693-A68E-4B89-A876-02161A604D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="60">
   <si>
     <t>register 1</t>
   </si>
@@ -821,16 +821,36 @@
       <c r="M4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
+      <c r="N4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -869,15 +889,36 @@
       <c r="M5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
+      <c r="N5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -916,16 +957,36 @@
       <c r="M6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
+      <c r="N6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="W6" s="3" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
@@ -1066,15 +1127,33 @@
       <c r="M10" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
+      <c r="N10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="W10" s="3"/>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
@@ -1112,15 +1191,34 @@
       <c r="M11" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="O11" s="3"/>
+      <c r="N11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
+      <c r="Q11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="U11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
@@ -1159,16 +1257,36 @@
       <c r="M12" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
+      <c r="N12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
@@ -1309,15 +1427,33 @@
       <c r="M16" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
+      <c r="N16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="U16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="W16" s="3"/>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
@@ -1355,15 +1491,34 @@
       <c r="M17" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="O17" s="3"/>
+      <c r="N17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
+      <c r="Q17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
@@ -1402,16 +1557,36 @@
       <c r="M18" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
+      <c r="N18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="24">
